--- a/data/Program Output KPIs by $.xlsx
+++ b/data/Program Output KPIs by $.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="350" documentId="8_{000ED4D8-2F13-49E0-B875-8A1913681784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{174E8003-1582-45F9-80A0-E7F4251D6037}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517A5F0F-26B7-4E58-A2FD-3CB4F273B473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -205,10 +205,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -493,7 +493,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -520,28 +520,28 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -550,10 +550,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -567,10 +567,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -594,10 +594,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -606,6 +606,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -616,24 +634,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -972,17 +972,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436DF3B9-9B26-4648-BD64-23BB8D8864D3}">
   <dimension ref="A1:I26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="66.6328125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="8.81640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" style="13" customWidth="1"/>
-    <col min="6" max="9" width="6.1796875" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="66.6640625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="9" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="13" customWidth="1"/>
+    <col min="6" max="9" width="6.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="41" customFormat="1" ht="36.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="41" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="40"/>
       <c r="B1" s="34" t="s">
         <v>20</v>
@@ -1009,14 +1009,14 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>52</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29">
-        <v>86973321.091999993</v>
+        <v>86973321.099999994</v>
       </c>
       <c r="E2" s="30"/>
       <c r="F2" s="30"/>
@@ -1025,7 +1025,7 @@
       <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="42" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="15" t="s">
@@ -1043,8 +1043,8 @@
       <c r="H3" s="18"/>
       <c r="I3" s="19"/>
     </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A4" s="47"/>
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A4" s="43"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
@@ -1060,8 +1060,8 @@
       <c r="H4" s="9"/>
       <c r="I4" s="20"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="48"/>
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="44"/>
       <c r="B5" s="21" t="s">
         <v>13</v>
       </c>
@@ -1078,17 +1078,17 @@
       <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="48" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>45</v>
       </c>
       <c r="D6" s="16">
-        <v>1.2992489947632229</v>
+        <v>1.3</v>
       </c>
       <c r="E6" s="17"/>
       <c r="F6" s="17"/>
@@ -1097,8 +1097,8 @@
       <c r="I6" s="19"/>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
-      <c r="B7" s="43"/>
+      <c r="A7" s="46"/>
+      <c r="B7" s="49"/>
       <c r="C7" s="7" t="s">
         <v>46</v>
       </c>
@@ -1112,15 +1112,15 @@
       <c r="I7" s="20"/>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A8" s="50"/>
-      <c r="B8" s="44" t="s">
+      <c r="A8" s="46"/>
+      <c r="B8" s="50" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>47</v>
       </c>
       <c r="D8" s="10">
-        <v>1.1842712076160351</v>
+        <v>1.2</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -1129,8 +1129,8 @@
       <c r="I8" s="20"/>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A9" s="50"/>
-      <c r="B9" s="44"/>
+      <c r="A9" s="46"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="8" t="s">
         <v>44</v>
       </c>
@@ -1144,15 +1144,15 @@
       <c r="I9" s="20"/>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="50"/>
-      <c r="B10" s="44" t="s">
+      <c r="A10" s="46"/>
+      <c r="B10" s="50" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="10">
-        <v>145.00998515003334</v>
+        <v>145</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
@@ -1161,8 +1161,8 @@
       <c r="I10" s="20"/>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A11" s="50"/>
-      <c r="B11" s="44"/>
+      <c r="A11" s="46"/>
+      <c r="B11" s="50"/>
       <c r="C11" s="8" t="s">
         <v>22</v>
       </c>
@@ -1176,15 +1176,15 @@
       <c r="I11" s="20"/>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A12" s="50"/>
-      <c r="B12" s="44" t="s">
+      <c r="A12" s="46"/>
+      <c r="B12" s="50" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="10">
-        <v>16.602792464053927</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -1192,9 +1192,9 @@
       <c r="H12" s="9"/>
       <c r="I12" s="20"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="51"/>
-      <c r="B13" s="45"/>
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="47"/>
+      <c r="B13" s="51"/>
       <c r="C13" s="37" t="s">
         <v>49</v>
       </c>
@@ -1208,7 +1208,7 @@
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="42" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="15" t="s">
@@ -1227,7 +1227,7 @@
       <c r="I14" s="19"/>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A15" s="47"/>
+      <c r="A15" s="43"/>
       <c r="B15" s="3" t="s">
         <v>32</v>
       </c>
@@ -1244,7 +1244,7 @@
       <c r="I15" s="20"/>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A16" s="47"/>
+      <c r="A16" s="43"/>
       <c r="B16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1261,7 +1261,7 @@
       <c r="I16" s="20"/>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A17" s="47"/>
+      <c r="A17" s="43"/>
       <c r="B17" s="3" t="s">
         <v>34</v>
       </c>
@@ -1277,8 +1277,8 @@
       <c r="H17" s="9"/>
       <c r="I17" s="20"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="48"/>
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="44"/>
       <c r="B18" s="21" t="s">
         <v>35</v>
       </c>
@@ -1286,7 +1286,7 @@
         <v>26</v>
       </c>
       <c r="D18" s="39">
-        <v>0.26444891043853208</v>
+        <v>0.3</v>
       </c>
       <c r="E18" s="23"/>
       <c r="F18" s="23"/>
@@ -1295,7 +1295,7 @@
       <c r="I18" s="25"/>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="42" t="s">
         <v>5</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -1305,7 +1305,7 @@
         <v>27</v>
       </c>
       <c r="D19" s="16">
-        <v>1.6096890200606302</v>
+        <v>1.6</v>
       </c>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
@@ -1314,7 +1314,7 @@
       <c r="I19" s="19"/>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="47"/>
+      <c r="A20" s="43"/>
       <c r="B20" s="3" t="s">
         <v>37</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>6</v>
       </c>
       <c r="D20" s="10">
-        <v>0.43691559115931389</v>
+        <v>0.44</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
@@ -1331,7 +1331,7 @@
       <c r="I20" s="20"/>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
+      <c r="A21" s="43"/>
       <c r="B21" s="3" t="s">
         <v>38</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>28</v>
       </c>
       <c r="D21" s="10">
-        <v>9.1982229717750288E-2</v>
+        <v>0.1</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
@@ -1348,7 +1348,7 @@
       <c r="I21" s="20"/>
     </row>
     <row r="22" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A22" s="47"/>
+      <c r="A22" s="43"/>
       <c r="B22" s="3" t="s">
         <v>39</v>
       </c>
@@ -1364,8 +1364,8 @@
       <c r="H22" s="9"/>
       <c r="I22" s="20"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="48"/>
+    <row r="23" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="44"/>
       <c r="B23" s="21" t="s">
         <v>40</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>31</v>
       </c>
       <c r="D23" s="39">
-        <v>0.34493336144156361</v>
+        <v>0.34</v>
       </c>
       <c r="E23" s="23"/>
       <c r="F23" s="23"/>
@@ -1382,7 +1382,7 @@
       <c r="I23" s="25"/>
     </row>
     <row r="24" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="42" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="15" t="s">
@@ -1401,7 +1401,7 @@
       <c r="I24" s="19"/>
     </row>
     <row r="25" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A25" s="47"/>
+      <c r="A25" s="43"/>
       <c r="B25" s="3" t="s">
         <v>42</v>
       </c>
@@ -1417,8 +1417,8 @@
       <c r="H25" s="9"/>
       <c r="I25" s="20"/>
     </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="48"/>
+    <row r="26" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="44"/>
       <c r="B26" s="21" t="s">
         <v>43</v>
       </c>
@@ -1436,6 +1436,7 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A24:A26"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A13"/>
     <mergeCell ref="A14:A18"/>
@@ -1444,7 +1445,6 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A24:A26"/>
   </mergeCells>
   <conditionalFormatting sqref="D3">
     <cfRule type="colorScale" priority="11">
@@ -1543,4 +1543,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/Program Output KPIs by $.xlsx
+++ b/data/Program Output KPIs by $.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517A5F0F-26B7-4E58-A2FD-3CB4F273B473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD3E469-3A85-4B12-A557-6F71167C74D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -1035,7 +1035,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="16">
-        <v>2.4950179810939765</v>
+        <v>2.5</v>
       </c>
       <c r="E3" s="17"/>
       <c r="F3" s="17"/>
@@ -1436,15 +1436,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A13"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A19:A23"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <conditionalFormatting sqref="D3">
     <cfRule type="colorScale" priority="11">

--- a/data/Program Output KPIs by $.xlsx
+++ b/data/Program Output KPIs by $.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD3E469-3A85-4B12-A557-6F71167C74D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="8_{1ED5F83D-CF3D-4D77-BA5A-C42CE2762578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31549331-05A7-4EF6-B20B-02D01F381349}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="54">
   <si>
     <t>Research Outputs</t>
   </si>
@@ -198,17 +198,19 @@
   </si>
   <si>
     <t>Total US Dollar ($)</t>
+  </si>
+  <si>
+    <t>Notional Target</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -282,7 +284,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -301,6 +303,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -493,9 +501,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -520,28 +528,22 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -550,10 +552,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -567,10 +566,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -594,10 +590,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -605,6 +598,36 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -971,468 +994,523 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436DF3B9-9B26-4648-BD64-23BB8D8864D3}">
-  <dimension ref="A1:I26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.109375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="66.6640625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="9" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="13" customWidth="1"/>
-    <col min="6" max="9" width="6.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.08984375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="66.6328125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="9.36328125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" style="46" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1796875" style="12" customWidth="1"/>
+    <col min="7" max="10" width="6.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="41" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40"/>
-      <c r="B1" s="34" t="s">
+    <row r="1" spans="1:10" s="36" customFormat="1" ht="36.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="35"/>
+      <c r="B1" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="35">
+      <c r="D1" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="44">
         <v>2025</v>
       </c>
-      <c r="E1" s="35">
+      <c r="F1" s="31">
         <v>2026</v>
       </c>
-      <c r="F1" s="35">
+      <c r="G1" s="31">
         <v>2027</v>
       </c>
-      <c r="G1" s="35">
+      <c r="H1" s="31">
         <v>2028</v>
       </c>
-      <c r="H1" s="35">
+      <c r="I1" s="31">
         <v>2029</v>
       </c>
-      <c r="I1" s="35">
+      <c r="J1" s="31">
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="29">
-        <v>86973321.099999994</v>
-      </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="33"/>
-    </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="B2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="45">
+        <v>86973321.091999993</v>
+      </c>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="29"/>
+    </row>
+    <row r="3" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A3" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="16">
-        <v>2.5</v>
-      </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="19"/>
-    </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="43"/>
+      <c r="D3" s="39">
+        <v>4</v>
+      </c>
+      <c r="E3" s="14">
+        <v>2.4950179810939765</v>
+      </c>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="17"/>
+    </row>
+    <row r="4" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A4" s="48"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="40"/>
+      <c r="E4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="9"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="20"/>
-    </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="44"/>
-      <c r="B5" s="21" t="s">
+      <c r="I4" s="9"/>
+      <c r="J4" s="18"/>
+    </row>
+    <row r="5" spans="1:10" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="41"/>
+      <c r="E5" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="25"/>
-    </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="22"/>
+    </row>
+    <row r="6" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A6" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="16">
-        <v>1.3</v>
-      </c>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A7" s="46"/>
-      <c r="B7" s="49"/>
+      <c r="D6" s="39">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14">
+        <v>1.2992489947632229</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="17"/>
+    </row>
+    <row r="7" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A7" s="51"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="40"/>
+      <c r="E7" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="9"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="20"/>
-    </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A8" s="46"/>
-      <c r="B8" s="50" t="s">
+      <c r="I7" s="9"/>
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A8" s="51"/>
+      <c r="B8" s="55" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="10">
-        <v>1.2</v>
-      </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="9"/>
+      <c r="D8" s="42">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10">
+        <v>1.1842712076160351</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A9" s="46"/>
-      <c r="B9" s="50"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="18"/>
+    </row>
+    <row r="9" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A9" s="51"/>
+      <c r="B9" s="55"/>
       <c r="C9" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="42"/>
+      <c r="E9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="9"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="20"/>
-    </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="46"/>
-      <c r="B10" s="50" t="s">
+      <c r="I9" s="9"/>
+      <c r="J9" s="18"/>
+    </row>
+    <row r="10" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A10" s="51"/>
+      <c r="B10" s="55" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="42">
         <v>145</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="9"/>
+      <c r="E10" s="10">
+        <v>145.00998515003334</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="20"/>
-    </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A11" s="46"/>
-      <c r="B11" s="50"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="18"/>
+    </row>
+    <row r="11" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A11" s="51"/>
+      <c r="B11" s="55"/>
       <c r="C11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="42"/>
+      <c r="E11" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="9"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="20"/>
-    </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A12" s="46"/>
-      <c r="B12" s="50" t="s">
+      <c r="I11" s="9"/>
+      <c r="J11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A12" s="51"/>
+      <c r="B12" s="55" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="10">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="9"/>
+      <c r="D12" s="42">
+        <v>16</v>
+      </c>
+      <c r="E12" s="10">
+        <v>16.602792464053927</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="20"/>
-    </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="47"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="37" t="s">
+      <c r="I12" s="9"/>
+      <c r="J12" s="18"/>
+    </row>
+    <row r="13" spans="1:10" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="52"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="43"/>
+      <c r="E13" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="25"/>
-    </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="42" t="s">
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="22"/>
+    </row>
+    <row r="14" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A14" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="39">
+        <v>0.3</v>
+      </c>
+      <c r="E14" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="19"/>
-    </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A15" s="43"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="17"/>
+    </row>
+    <row r="15" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A15" s="48"/>
       <c r="B15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="42"/>
+      <c r="E15" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="9"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="20"/>
-    </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A16" s="43"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A16" s="48"/>
       <c r="B16" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="42"/>
+      <c r="E16" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="9"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="20"/>
-    </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A17" s="43"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A17" s="48"/>
       <c r="B17" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="40">
+        <v>0.6</v>
+      </c>
+      <c r="E17" s="10">
         <v>0.58638671445065815</v>
       </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="9"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="20"/>
-    </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44"/>
-      <c r="B18" s="21" t="s">
+      <c r="I17" s="9"/>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" spans="1:10" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="49"/>
+      <c r="B18" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="39">
-        <v>0.3</v>
-      </c>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="25"/>
-    </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A19" s="42" t="s">
+      <c r="D18" s="41">
+        <v>0.31</v>
+      </c>
+      <c r="E18" s="34">
+        <v>0.26444891043853208</v>
+      </c>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="22"/>
+    </row>
+    <row r="19" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A19" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="39">
         <v>1.6</v>
       </c>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
-    </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="43"/>
+      <c r="E19" s="14">
+        <v>1.6096890200606302</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="17"/>
+    </row>
+    <row r="20" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A20" s="48"/>
       <c r="B20" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="10">
-        <v>0.44</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="9"/>
+      <c r="D20" s="40">
+        <v>0.4</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0.43691559115931389</v>
+      </c>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="20"/>
-    </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="43"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A21" s="48"/>
       <c r="B21" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="9"/>
+      <c r="D21" s="40">
+        <v>0.13</v>
+      </c>
+      <c r="E21" s="10">
+        <v>9.1982229717750288E-2</v>
+      </c>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="20"/>
-    </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A22" s="43"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A22" s="48"/>
       <c r="B22" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="40">
+        <v>0.33</v>
+      </c>
+      <c r="E22" s="10">
         <v>0.21</v>
       </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="9"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="20"/>
-    </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="44"/>
-      <c r="B23" s="21" t="s">
+      <c r="I22" s="9"/>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="1:10" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="49"/>
+      <c r="B23" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="39">
-        <v>0.34</v>
-      </c>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="25"/>
-    </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A24" s="42" t="s">
+      <c r="D23" s="43">
+        <v>0.22550000000000001</v>
+      </c>
+      <c r="E23" s="34">
+        <v>0.34493336144156361</v>
+      </c>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="22"/>
+    </row>
+    <row r="24" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A24" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D24" s="39"/>
+      <c r="E24" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="19"/>
-    </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A25" s="43"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="17"/>
+    </row>
+    <row r="25" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A25" s="48"/>
       <c r="B25" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="40"/>
+      <c r="E25" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="9"/>
+      <c r="F25" s="11"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="20"/>
-    </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="44"/>
-      <c r="B26" s="21" t="s">
+      <c r="I25" s="9"/>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="49"/>
+      <c r="B26" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="41"/>
+      <c r="E26" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="23"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="25"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1446,11 +1524,11 @@
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A19:A23"/>
   </mergeCells>
-  <conditionalFormatting sqref="D3">
-    <cfRule type="colorScale" priority="11">
+  <conditionalFormatting sqref="E3">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="131/$D$2"/>
+        <cfvo type="formula" val="131/$E$2"/>
         <cfvo type="num" val="4"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
@@ -1458,82 +1536,128 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="E6">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="75/$D$2"/>
-        <cfvo type="formula" val="150/$D$2"/>
+        <cfvo type="formula" val="$D$6/2"/>
+        <cfvo type="formula" val="$D$6"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8">
-    <cfRule type="colorScale" priority="9">
+  <conditionalFormatting sqref="E8">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="30/$D$2"/>
-        <cfvo type="formula" val="103/$D$2"/>
+        <cfvo type="formula" val="$D$8/2"/>
+        <cfvo type="formula" val="$D$8"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D10">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="E10">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="6000/$D$2"/>
-        <cfvo type="formula" val="145"/>
+        <cfvo type="formula" val="$D$10/2"/>
+        <cfvo type="formula" val="$D$10"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D12">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="E12">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="16.600000000000001"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D17">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="10/$D$2"/>
-        <cfvo type="num" val="#REF!/$D$2"/>
+        <cfvo type="formula" val="$D$12/2"/>
+        <cfvo type="formula" val="$D$12"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18:D21 D23">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="E17">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
-        <cfvo type="num" val="0.08"/>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.4"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$17/2"/>
+        <cfvo type="num" val="$D$17"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D22">
+  <conditionalFormatting sqref="E18">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="formula" val="$D$18/2"/>
+        <cfvo type="formula" val="$D$18"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$19/2"/>
+        <cfvo type="formula" val="$D$19"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$20/2"/>
+        <cfvo type="formula" val="$D$20"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21">
     <cfRule type="colorScale" priority="1">
       <colorScale>
+        <cfvo type="formula" val="$D$21/2"/>
+        <cfvo type="formula" val="$D$21"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E22">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.7"/>
+        <cfvo type="formula" val="$D$22/2"/>
+        <cfvo type="formula" val="$D$22"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E23">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$23/2"/>
+        <cfvo type="formula" val="$D$23"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
@@ -1543,10 +1667,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>
--- a/data/Program Output KPIs by $.xlsx
+++ b/data/Program Output KPIs by $.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z003vm8n\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="8_{1ED5F83D-CF3D-4D77-BA5A-C42CE2762578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31549331-05A7-4EF6-B20B-02D01F381349}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B46F50E-B8B4-4F2D-A93C-88CDCA4482E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -208,9 +208,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -501,7 +501,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -528,22 +528,22 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -552,7 +552,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -566,7 +566,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -590,7 +590,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -620,13 +620,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -995,18 +995,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436DF3B9-9B26-4648-BD64-23BB8D8864D3}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="66.6328125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="9.36328125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="10.08984375" style="46" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1796875" style="12" customWidth="1"/>
-    <col min="7" max="10" width="6.1796875" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="66.6640625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11" style="46" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.21875" style="12" customWidth="1"/>
+    <col min="7" max="10" width="6.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="36" customFormat="1" ht="36.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" s="36" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="35"/>
       <c r="B1" s="30" t="s">
         <v>20</v>
@@ -1036,7 +1036,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>52</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="14">
         <v>2.4950179810939765</v>
@@ -1074,7 +1074,7 @@
       <c r="I3" s="16"/>
       <c r="J3" s="17"/>
     </row>
-    <row r="4" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="48"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
@@ -1092,7 +1092,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="18"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
       <c r="B5" s="19" t="s">
         <v>13</v>
@@ -1240,7 +1240,7 @@
       <c r="I12" s="9"/>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="52"/>
       <c r="B13" s="56"/>
       <c r="C13" s="33" t="s">
@@ -1334,7 +1334,7 @@
       <c r="I17" s="9"/>
       <c r="J17" s="18"/>
     </row>
-    <row r="18" spans="1:10" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="49"/>
       <c r="B18" s="19" t="s">
         <v>35</v>
@@ -1436,7 +1436,7 @@
       <c r="I22" s="9"/>
       <c r="J22" s="18"/>
     </row>
-    <row r="23" spans="1:10" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="49"/>
       <c r="B23" s="19" t="s">
         <v>40</v>
@@ -1494,7 +1494,7 @@
       <c r="I25" s="9"/>
       <c r="J25" s="18"/>
     </row>
-    <row r="26" spans="1:10" s="2" customFormat="1" ht="12.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="49"/>
       <c r="B26" s="19" t="s">
         <v>43</v>
@@ -1514,22 +1514,22 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A13"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A19:A23"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="131/$E$2"/>
-        <cfvo type="num" val="4"/>
+        <cfvo type="formula" val="$D$3/2"/>
+        <cfvo type="formula" val="$D$3"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
@@ -1667,4 +1667,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/Program Output KPIs by $.xlsx
+++ b/data/Program Output KPIs by $.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z003vm8n\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B46F50E-B8B4-4F2D-A93C-88CDCA4482E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFD07C1-DABF-418E-B794-6CA0B30E8AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -107,9 +107,6 @@
     <t>Number of delivery partners trained</t>
   </si>
   <si>
-    <t>Number of delivery partners trained who are female</t>
-  </si>
-  <si>
     <t>Number of varieties released</t>
   </si>
   <si>
@@ -188,9 +185,6 @@
     <t>Number of national scientists who attended training courses</t>
   </si>
   <si>
-    <t>Number of national scientists who attended training courses who are female</t>
-  </si>
-  <si>
     <t>KPI Metric</t>
   </si>
   <si>
@@ -201,6 +195,12 @@
   </si>
   <si>
     <t>Notional Target</t>
+  </si>
+  <si>
+    <t>Percentage of delivery partners trained who are female</t>
+  </si>
+  <si>
+    <t>Percentage of national scientists who attended training courses who are female</t>
   </si>
 </sst>
 </file>
@@ -1012,10 +1012,10 @@
         <v>20</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E1" s="44">
         <v>2025</v>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B2" s="24"/>
       <c r="C2" s="25"/>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D4" s="40"/>
       <c r="E4" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="D5" s="41"/>
       <c r="E5" s="34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F5" s="20"/>
       <c r="G5" s="20"/>
@@ -1118,7 +1118,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="39">
         <v>1</v>
@@ -1136,11 +1136,11 @@
       <c r="A7" s="51"/>
       <c r="B7" s="54"/>
       <c r="C7" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="40"/>
       <c r="E7" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
@@ -1154,7 +1154,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="42">
         <v>1</v>
@@ -1172,11 +1172,11 @@
       <c r="A9" s="51"/>
       <c r="B9" s="55"/>
       <c r="C9" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" s="42"/>
       <c r="E9" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
@@ -1208,11 +1208,11 @@
       <c r="A11" s="51"/>
       <c r="B11" s="55"/>
       <c r="C11" s="8" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="D11" s="42"/>
       <c r="E11" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
@@ -1226,7 +1226,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" s="42">
         <v>16</v>
@@ -1244,11 +1244,11 @@
       <c r="A13" s="52"/>
       <c r="B13" s="56"/>
       <c r="C13" s="33" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D13" s="43"/>
       <c r="E13" s="34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
@@ -1261,16 +1261,16 @@
         <v>3</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" s="39">
         <v>0.3</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
@@ -1281,14 +1281,14 @@
     <row r="15" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A15" s="48"/>
       <c r="B15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="42"/>
       <c r="E15" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
@@ -1299,14 +1299,14 @@
     <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A16" s="48"/>
       <c r="B16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="42"/>
       <c r="E16" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
@@ -1317,7 +1317,7 @@
     <row r="17" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A17" s="48"/>
       <c r="B17" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
@@ -1337,10 +1337,10 @@
     <row r="18" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="49"/>
       <c r="B18" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" s="41">
         <v>0.31</v>
@@ -1359,10 +1359,10 @@
         <v>5</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" s="39">
         <v>1.6</v>
@@ -1379,7 +1379,7 @@
     <row r="20" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A20" s="48"/>
       <c r="B20" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>6</v>
@@ -1399,10 +1399,10 @@
     <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A21" s="48"/>
       <c r="B21" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" s="40">
         <v>0.13</v>
@@ -1419,10 +1419,10 @@
     <row r="22" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A22" s="48"/>
       <c r="B22" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="40">
         <v>0.33</v>
@@ -1439,10 +1439,10 @@
     <row r="23" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="49"/>
       <c r="B23" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" s="43">
         <v>0.22550000000000001</v>
@@ -1461,14 +1461,14 @@
         <v>7</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="39"/>
       <c r="E24" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F24" s="15"/>
       <c r="G24" s="16"/>
@@ -1479,14 +1479,14 @@
     <row r="25" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A25" s="48"/>
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="40"/>
       <c r="E25" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F25" s="11"/>
       <c r="G25" s="9"/>
@@ -1497,14 +1497,14 @@
     <row r="26" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="49"/>
       <c r="B26" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="41"/>
       <c r="E26" s="34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F26" s="20"/>
       <c r="G26" s="21"/>
@@ -1514,15 +1514,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A13"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A19:A23"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
     <cfRule type="colorScale" priority="17">

--- a/data/Program Output KPIs by $.xlsx
+++ b/data/Program Output KPIs by $.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFD07C1-DABF-418E-B794-6CA0B30E8AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0147887-B1DF-4D89-AD11-FC006CE53CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -110,9 +110,6 @@
     <t>Number of varieties released</t>
   </si>
   <si>
-    <t>Percentage of annual rate of genetic gain, by crop</t>
-  </si>
-  <si>
     <t>Crop Trust performance compliance rate (%)</t>
   </si>
   <si>
@@ -201,6 +198,9 @@
   </si>
   <si>
     <t>Percentage of national scientists who attended training courses who are female</t>
+  </si>
+  <si>
+    <t>Average (across crops) percentage yield-related genetic gain</t>
   </si>
 </sst>
 </file>
@@ -629,6 +629,18 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -645,18 +657,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1012,10 +1012,10 @@
         <v>20</v>
       </c>
       <c r="C1" s="30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E1" s="44">
         <v>2025</v>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="24"/>
       <c r="C2" s="25"/>
@@ -1053,7 +1053,7 @@
       <c r="J2" s="29"/>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="51" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -1075,7 +1075,7 @@
       <c r="J3" s="17"/>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="48"/>
+      <c r="A4" s="52"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D4" s="40"/>
       <c r="E4" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
@@ -1093,7 +1093,7 @@
       <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="49"/>
+      <c r="A5" s="53"/>
       <c r="B5" s="19" t="s">
         <v>13</v>
       </c>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="D5" s="41"/>
       <c r="E5" s="34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" s="20"/>
       <c r="G5" s="20"/>
@@ -1111,14 +1111,14 @@
       <c r="J5" s="22"/>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="47" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" s="39">
         <v>1</v>
@@ -1133,14 +1133,14 @@
       <c r="J6" s="17"/>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
-      <c r="B7" s="54"/>
+      <c r="A7" s="55"/>
+      <c r="B7" s="48"/>
       <c r="C7" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="40"/>
       <c r="E7" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
@@ -1149,12 +1149,12 @@
       <c r="J7" s="18"/>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
-      <c r="B8" s="55" t="s">
+      <c r="A8" s="55"/>
+      <c r="B8" s="49" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" s="42">
         <v>1</v>
@@ -1169,14 +1169,14 @@
       <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
-      <c r="B9" s="55"/>
+      <c r="A9" s="55"/>
+      <c r="B9" s="49"/>
       <c r="C9" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="42"/>
       <c r="E9" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
@@ -1185,8 +1185,8 @@
       <c r="J9" s="18"/>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
-      <c r="B10" s="55" t="s">
+      <c r="A10" s="55"/>
+      <c r="B10" s="49" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -1205,14 +1205,14 @@
       <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A11" s="51"/>
-      <c r="B11" s="55"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="42"/>
       <c r="E11" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
@@ -1221,12 +1221,12 @@
       <c r="J11" s="18"/>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A12" s="51"/>
-      <c r="B12" s="55" t="s">
+      <c r="A12" s="55"/>
+      <c r="B12" s="49" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" s="42">
         <v>16</v>
@@ -1241,14 +1241,14 @@
       <c r="J12" s="18"/>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="52"/>
-      <c r="B13" s="56"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="50"/>
       <c r="C13" s="33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="43"/>
       <c r="E13" s="34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
@@ -1257,11 +1257,11 @@
       <c r="J13" s="22"/>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="51" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>22</v>
@@ -1270,7 +1270,7 @@
         <v>0.3</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
@@ -1279,16 +1279,16 @@
       <c r="J14" s="17"/>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A15" s="48"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D15" s="42"/>
       <c r="E15" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
@@ -1297,16 +1297,16 @@
       <c r="J15" s="18"/>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A16" s="48"/>
+      <c r="A16" s="52"/>
       <c r="B16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" s="42"/>
       <c r="E16" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
@@ -1315,9 +1315,9 @@
       <c r="J16" s="18"/>
     </row>
     <row r="17" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A17" s="48"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
@@ -1335,12 +1335,12 @@
       <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="49"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" s="41">
         <v>0.31</v>
@@ -1355,14 +1355,14 @@
       <c r="J18" s="22"/>
     </row>
     <row r="19" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="51" t="s">
         <v>5</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" s="39">
         <v>1.6</v>
@@ -1377,9 +1377,9 @@
       <c r="J19" s="17"/>
     </row>
     <row r="20" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="48"/>
+      <c r="A20" s="52"/>
       <c r="B20" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>6</v>
@@ -1397,12 +1397,12 @@
       <c r="J20" s="18"/>
     </row>
     <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
+      <c r="A21" s="52"/>
       <c r="B21" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21" s="40">
         <v>0.13</v>
@@ -1417,12 +1417,12 @@
       <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A22" s="48"/>
+      <c r="A22" s="52"/>
       <c r="B22" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" s="40">
         <v>0.33</v>
@@ -1437,12 +1437,12 @@
       <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="49"/>
+      <c r="A23" s="53"/>
       <c r="B23" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" s="43">
         <v>0.22550000000000001</v>
@@ -1457,18 +1457,18 @@
       <c r="J23" s="22"/>
     </row>
     <row r="24" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A24" s="47" t="s">
+      <c r="A24" s="51" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="39"/>
       <c r="E24" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F24" s="15"/>
       <c r="G24" s="16"/>
@@ -1477,16 +1477,16 @@
       <c r="J24" s="17"/>
     </row>
     <row r="25" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A25" s="48"/>
+      <c r="A25" s="52"/>
       <c r="B25" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="40"/>
       <c r="E25" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F25" s="11"/>
       <c r="G25" s="9"/>
@@ -1495,16 +1495,16 @@
       <c r="J25" s="18"/>
     </row>
     <row r="26" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="49"/>
+      <c r="A26" s="53"/>
       <c r="B26" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="41"/>
       <c r="E26" s="34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F26" s="20"/>
       <c r="G26" s="21"/>
@@ -1514,15 +1514,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A19:A23"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="A19:A23"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
     <cfRule type="colorScale" priority="17">

--- a/data/Program Output KPIs by $.xlsx
+++ b/data/Program Output KPIs by $.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0147887-B1DF-4D89-AD11-FC006CE53CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5609835-1175-422A-AA84-5B8DDF2B28F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Research Outputs</t>
   </si>
@@ -207,10 +207,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -284,7 +286,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -309,6 +311,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -499,11 +507,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -557,27 +566,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -602,9 +590,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -619,16 +604,97 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -641,31 +707,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF79B907"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1001,59 +1055,59 @@
     <col min="2" max="2" width="12.77734375" style="5" customWidth="1"/>
     <col min="3" max="3" width="66.6640625" style="5" customWidth="1"/>
     <col min="4" max="4" width="9.33203125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="11" style="46" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" style="36" customWidth="1"/>
     <col min="6" max="6" width="6.21875" style="12" customWidth="1"/>
     <col min="7" max="10" width="6.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="36" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35"/>
-      <c r="B1" s="30" t="s">
+    <row r="1" spans="1:10" s="29" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="28"/>
+      <c r="B1" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="44">
+      <c r="E1" s="24">
         <v>2025</v>
       </c>
-      <c r="F1" s="31">
+      <c r="F1" s="24">
         <v>2026</v>
       </c>
-      <c r="G1" s="31">
+      <c r="G1" s="24">
         <v>2027</v>
       </c>
-      <c r="H1" s="31">
+      <c r="H1" s="24">
         <v>2028</v>
       </c>
-      <c r="I1" s="31">
+      <c r="I1" s="24">
         <v>2029</v>
       </c>
-      <c r="J1" s="31">
+      <c r="J1" s="24">
         <v>2030</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="45">
+      <c r="B2" s="38"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="40">
         <v>86973321.091999993</v>
       </c>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="29"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="60" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -1062,10 +1116,11 @@
       <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="31">
         <v>3</v>
       </c>
       <c r="E3" s="14">
+        <f>217/E2*1000000</f>
         <v>2.4950179810939765</v>
       </c>
       <c r="F3" s="15"/>
@@ -1075,14 +1130,14 @@
       <c r="J3" s="17"/>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="52"/>
+      <c r="A4" s="61"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="40"/>
+      <c r="D4" s="32"/>
       <c r="E4" s="10" t="s">
         <v>48</v>
       </c>
@@ -1093,16 +1148,19 @@
       <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="53"/>
+      <c r="A5" s="62"/>
       <c r="B5" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="41"/>
-      <c r="E5" s="34" t="s">
-        <v>48</v>
+      <c r="D5" s="33">
+        <v>0.11</v>
+      </c>
+      <c r="E5" s="45">
+        <f>6/E2*1000000</f>
+        <v>6.898667228831272E-2</v>
       </c>
       <c r="F5" s="20"/>
       <c r="G5" s="20"/>
@@ -1111,16 +1169,16 @@
       <c r="J5" s="22"/>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="66" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="31">
         <v>1</v>
       </c>
       <c r="E6" s="14">
@@ -1133,14 +1191,16 @@
       <c r="J6" s="17"/>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A7" s="55"/>
-      <c r="B7" s="48"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="67"/>
       <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="40"/>
-      <c r="E7" s="10" t="s">
-        <v>48</v>
+      <c r="D7" s="46">
+        <v>0.59</v>
+      </c>
+      <c r="E7" s="47">
+        <v>0.59</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
@@ -1149,14 +1209,14 @@
       <c r="J7" s="18"/>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A8" s="55"/>
-      <c r="B8" s="49" t="s">
+      <c r="A8" s="64"/>
+      <c r="B8" s="68" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="34">
         <v>1</v>
       </c>
       <c r="E8" s="10">
@@ -1169,14 +1229,16 @@
       <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A9" s="55"/>
-      <c r="B9" s="49"/>
+      <c r="A9" s="64"/>
+      <c r="B9" s="68"/>
       <c r="C9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="42"/>
-      <c r="E9" s="10" t="s">
-        <v>48</v>
+      <c r="D9" s="48">
+        <v>0.49</v>
+      </c>
+      <c r="E9" s="47">
+        <v>0.49</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
@@ -1185,14 +1247,14 @@
       <c r="J9" s="18"/>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="55"/>
-      <c r="B10" s="49" t="s">
+      <c r="A10" s="64"/>
+      <c r="B10" s="68" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="34">
         <v>145</v>
       </c>
       <c r="E10" s="10">
@@ -1205,14 +1267,16 @@
       <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A11" s="55"/>
-      <c r="B11" s="49"/>
+      <c r="A11" s="64"/>
+      <c r="B11" s="68"/>
       <c r="C11" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="42"/>
-      <c r="E11" s="10" t="s">
-        <v>48</v>
+      <c r="D11" s="50">
+        <v>0.8</v>
+      </c>
+      <c r="E11" s="47">
+        <v>0.44</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
@@ -1221,14 +1285,14 @@
       <c r="J11" s="18"/>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A12" s="55"/>
-      <c r="B12" s="49" t="s">
+      <c r="A12" s="64"/>
+      <c r="B12" s="68" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="34">
         <v>16</v>
       </c>
       <c r="E12" s="10">
@@ -1241,14 +1305,16 @@
       <c r="J12" s="18"/>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="56"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="33" t="s">
+      <c r="A13" s="65"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="43"/>
-      <c r="E13" s="34" t="s">
-        <v>48</v>
+      <c r="D13" s="51">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="49">
+        <v>0.34</v>
       </c>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
@@ -1257,7 +1323,7 @@
       <c r="J13" s="22"/>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="13" t="s">
@@ -1266,11 +1332,12 @@
       <c r="C14" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="39">
-        <v>0.3</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>48</v>
+      <c r="D14" s="31">
+        <v>0.5</v>
+      </c>
+      <c r="E14" s="14">
+        <f>46/E2*1000000</f>
+        <v>0.52889782087706416</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
@@ -1279,16 +1346,18 @@
       <c r="J14" s="17"/>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="10" t="s">
-        <v>48</v>
+      <c r="D15" s="52">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E15" s="53">
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
@@ -1297,16 +1366,18 @@
       <c r="J15" s="18"/>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A16" s="52"/>
+      <c r="A16" s="61"/>
       <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="10" t="s">
-        <v>48</v>
+      <c r="D16" s="50">
+        <v>1</v>
+      </c>
+      <c r="E16" s="47">
+        <v>1</v>
       </c>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
@@ -1315,14 +1386,14 @@
       <c r="J16" s="18"/>
     </row>
     <row r="17" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A17" s="52"/>
+      <c r="A17" s="61"/>
       <c r="B17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="32">
         <v>0.6</v>
       </c>
       <c r="E17" s="10">
@@ -1335,17 +1406,17 @@
       <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="53"/>
+      <c r="A18" s="62"/>
       <c r="B18" s="19" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="33">
         <v>0.31</v>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="27">
         <v>0.26444891043853208</v>
       </c>
       <c r="F18" s="20"/>
@@ -1355,7 +1426,7 @@
       <c r="J18" s="22"/>
     </row>
     <row r="19" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A19" s="51" t="s">
+      <c r="A19" s="60" t="s">
         <v>5</v>
       </c>
       <c r="B19" s="13" t="s">
@@ -1364,7 +1435,7 @@
       <c r="C19" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="31">
         <v>1.6</v>
       </c>
       <c r="E19" s="14">
@@ -1377,14 +1448,14 @@
       <c r="J19" s="17"/>
     </row>
     <row r="20" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="52"/>
+      <c r="A20" s="61"/>
       <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="32">
         <v>0.4</v>
       </c>
       <c r="E20" s="10">
@@ -1397,14 +1468,14 @@
       <c r="J20" s="18"/>
     </row>
     <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
+      <c r="A21" s="61"/>
       <c r="B21" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="32">
         <v>0.13</v>
       </c>
       <c r="E21" s="10">
@@ -1417,14 +1488,14 @@
       <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A22" s="52"/>
+      <c r="A22" s="61"/>
       <c r="B22" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="32">
         <v>0.33</v>
       </c>
       <c r="E22" s="10">
@@ -1437,17 +1508,17 @@
       <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="53"/>
+      <c r="A23" s="62"/>
       <c r="B23" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C23" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="43">
+      <c r="D23" s="35">
         <v>0.22550000000000001</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="27">
         <v>0.34493336144156361</v>
       </c>
       <c r="F23" s="20"/>
@@ -1457,7 +1528,7 @@
       <c r="J23" s="22"/>
     </row>
     <row r="24" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="60" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="13" t="s">
@@ -1466,9 +1537,11 @@
       <c r="C24" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="39"/>
-      <c r="E24" s="14" t="s">
-        <v>48</v>
+      <c r="D24" s="54">
+        <v>0.42</v>
+      </c>
+      <c r="E24" s="55">
+        <v>0.42</v>
       </c>
       <c r="F24" s="15"/>
       <c r="G24" s="16"/>
@@ -1477,16 +1550,18 @@
       <c r="J24" s="17"/>
     </row>
     <row r="25" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A25" s="52"/>
+      <c r="A25" s="61"/>
       <c r="B25" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="40"/>
-      <c r="E25" s="10" t="s">
-        <v>48</v>
+      <c r="D25" s="56">
+        <v>0.36</v>
+      </c>
+      <c r="E25" s="57">
+        <v>0.36</v>
       </c>
       <c r="F25" s="11"/>
       <c r="G25" s="9"/>
@@ -1495,16 +1570,18 @@
       <c r="J25" s="18"/>
     </row>
     <row r="26" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="53"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="19" t="s">
         <v>41</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="41"/>
-      <c r="E26" s="34" t="s">
-        <v>48</v>
+      <c r="D26" s="58">
+        <v>0.13</v>
+      </c>
+      <c r="E26" s="59">
+        <v>0.11</v>
       </c>
       <c r="F26" s="20"/>
       <c r="G26" s="21"/>
@@ -1514,18 +1591,18 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="A19:A23"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A19:A23"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$3/2"/>
@@ -1536,8 +1613,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E5">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$5/2"/>
+        <cfvo type="formula" val="$D$5"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="colorScale" priority="16">
+    <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$6/2"/>
@@ -1548,8 +1637,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$7/2"/>
+        <cfvo type="formula" val="$D$7"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$8/2"/>
@@ -1560,8 +1661,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$9/2"/>
+        <cfvo type="formula" val="$D$9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$10/2"/>
@@ -1572,8 +1685,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E11">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="$D$11/2"/>
+        <cfvo type="formula" val="$D$11"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E12">
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$12/2"/>
@@ -1584,8 +1707,54 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="formula" val="$D$13/2"/>
+        <cfvo type="formula" val="$D$13"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF79B907"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$14/2"/>
+        <cfvo type="formula" val="$D$14"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$15/2"/>
+        <cfvo type="formula" val="$D$15"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$16/2"/>
+        <cfvo type="formula" val="$D$16"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$17/2"/>
@@ -1597,7 +1766,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E18">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="formula" val="$D$18/2"/>
         <cfvo type="formula" val="$D$18"/>
@@ -1607,7 +1776,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$D$19/2"/>
@@ -1619,7 +1788,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$D$20/2"/>
@@ -1631,7 +1800,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="$D$21/2"/>
         <cfvo type="formula" val="$D$21"/>
@@ -1641,7 +1810,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="formula" val="$D$22/2"/>
@@ -1653,11 +1822,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="formula" val="$D$23/2"/>
         <cfvo type="formula" val="$D$23"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E24">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$24/2"/>
+        <cfvo type="formula" val="$D$24"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E25">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$25/2"/>
+        <cfvo type="formula" val="$D$25"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E26">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$D$26/2"/>
+        <cfvo type="formula" val="$D$26"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>

--- a/data/Program Output KPIs by $.xlsx
+++ b/data/Program Output KPIs by $.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5609835-1175-422A-AA84-5B8DDF2B28F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DBA049-1B96-46C5-A68D-9689E81FF2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -677,6 +677,18 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -693,18 +705,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1107,7 +1107,7 @@
       <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="64" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -1130,7 +1130,7 @@
       <c r="J3" s="17"/>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="61"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
@@ -1148,7 +1148,7 @@
       <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="62"/>
+      <c r="A5" s="66"/>
       <c r="B5" s="19" t="s">
         <v>13</v>
       </c>
@@ -1169,17 +1169,17 @@
       <c r="J5" s="22"/>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="60" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>43</v>
       </c>
       <c r="D6" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="14">
         <v>1.2992489947632229</v>
@@ -1191,8 +1191,8 @@
       <c r="J6" s="17"/>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A7" s="64"/>
-      <c r="B7" s="67"/>
+      <c r="A7" s="68"/>
+      <c r="B7" s="61"/>
       <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
@@ -1209,8 +1209,8 @@
       <c r="J7" s="18"/>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A8" s="64"/>
-      <c r="B8" s="68" t="s">
+      <c r="A8" s="68"/>
+      <c r="B8" s="62" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1229,8 +1229,8 @@
       <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A9" s="64"/>
-      <c r="B9" s="68"/>
+      <c r="A9" s="68"/>
+      <c r="B9" s="62"/>
       <c r="C9" s="8" t="s">
         <v>42</v>
       </c>
@@ -1247,8 +1247,8 @@
       <c r="J9" s="18"/>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="64"/>
-      <c r="B10" s="68" t="s">
+      <c r="A10" s="68"/>
+      <c r="B10" s="62" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -1267,8 +1267,8 @@
       <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A11" s="64"/>
-      <c r="B11" s="68"/>
+      <c r="A11" s="68"/>
+      <c r="B11" s="62"/>
       <c r="C11" s="8" t="s">
         <v>51</v>
       </c>
@@ -1285,8 +1285,8 @@
       <c r="J11" s="18"/>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A12" s="64"/>
-      <c r="B12" s="68" t="s">
+      <c r="A12" s="68"/>
+      <c r="B12" s="62" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -1305,8 +1305,8 @@
       <c r="J12" s="18"/>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="65"/>
-      <c r="B13" s="69"/>
+      <c r="A13" s="69"/>
+      <c r="B13" s="63"/>
       <c r="C13" s="26" t="s">
         <v>52</v>
       </c>
@@ -1323,7 +1323,7 @@
       <c r="J13" s="22"/>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="64" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="13" t="s">
@@ -1346,7 +1346,7 @@
       <c r="J14" s="17"/>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A15" s="61"/>
+      <c r="A15" s="65"/>
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
@@ -1366,7 +1366,7 @@
       <c r="J15" s="18"/>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A16" s="61"/>
+      <c r="A16" s="65"/>
       <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
@@ -1386,7 +1386,7 @@
       <c r="J16" s="18"/>
     </row>
     <row r="17" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A17" s="61"/>
+      <c r="A17" s="65"/>
       <c r="B17" s="3" t="s">
         <v>32</v>
       </c>
@@ -1406,7 +1406,7 @@
       <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="62"/>
+      <c r="A18" s="66"/>
       <c r="B18" s="19" t="s">
         <v>33</v>
       </c>
@@ -1426,7 +1426,7 @@
       <c r="J18" s="22"/>
     </row>
     <row r="19" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="64" t="s">
         <v>5</v>
       </c>
       <c r="B19" s="13" t="s">
@@ -1448,7 +1448,7 @@
       <c r="J19" s="17"/>
     </row>
     <row r="20" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="61"/>
+      <c r="A20" s="65"/>
       <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
@@ -1468,7 +1468,7 @@
       <c r="J20" s="18"/>
     </row>
     <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="61"/>
+      <c r="A21" s="65"/>
       <c r="B21" s="3" t="s">
         <v>36</v>
       </c>
@@ -1488,7 +1488,7 @@
       <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A22" s="61"/>
+      <c r="A22" s="65"/>
       <c r="B22" s="3" t="s">
         <v>37</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>28</v>
       </c>
       <c r="D22" s="32">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="E22" s="10">
         <v>0.21</v>
@@ -1508,7 +1508,7 @@
       <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="62"/>
+      <c r="A23" s="66"/>
       <c r="B23" s="19" t="s">
         <v>38</v>
       </c>
@@ -1528,7 +1528,7 @@
       <c r="J23" s="22"/>
     </row>
     <row r="24" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A24" s="60" t="s">
+      <c r="A24" s="64" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="13" t="s">
@@ -1550,7 +1550,7 @@
       <c r="J24" s="17"/>
     </row>
     <row r="25" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A25" s="61"/>
+      <c r="A25" s="65"/>
       <c r="B25" s="3" t="s">
         <v>40</v>
       </c>
@@ -1570,7 +1570,7 @@
       <c r="J25" s="18"/>
     </row>
     <row r="26" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="62"/>
+      <c r="A26" s="66"/>
       <c r="B26" s="19" t="s">
         <v>41</v>
       </c>
@@ -1591,15 +1591,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A19:A23"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="A19:A23"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
     <cfRule type="colorScale" priority="28">

--- a/data/Program Output KPIs by $.xlsx
+++ b/data/Program Output KPIs by $.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DBA049-1B96-46C5-A68D-9689E81FF2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C33D24-EA7E-4594-908F-7CCEAC3633EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -677,6 +677,24 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -687,24 +705,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1107,7 +1107,7 @@
       <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="60" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -1130,7 +1130,7 @@
       <c r="J3" s="17"/>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
+      <c r="A4" s="61"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
@@ -1148,7 +1148,7 @@
       <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="66"/>
+      <c r="A5" s="62"/>
       <c r="B5" s="19" t="s">
         <v>13</v>
       </c>
@@ -1169,10 +1169,10 @@
       <c r="J5" s="22"/>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="60" t="s">
+      <c r="B6" s="66" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="13" t="s">
@@ -1191,8 +1191,8 @@
       <c r="J6" s="17"/>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A7" s="68"/>
-      <c r="B7" s="61"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="67"/>
       <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
@@ -1209,8 +1209,8 @@
       <c r="J7" s="18"/>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A8" s="68"/>
-      <c r="B8" s="62" t="s">
+      <c r="A8" s="64"/>
+      <c r="B8" s="68" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1229,8 +1229,8 @@
       <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A9" s="68"/>
-      <c r="B9" s="62"/>
+      <c r="A9" s="64"/>
+      <c r="B9" s="68"/>
       <c r="C9" s="8" t="s">
         <v>42</v>
       </c>
@@ -1247,8 +1247,8 @@
       <c r="J9" s="18"/>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="68"/>
-      <c r="B10" s="62" t="s">
+      <c r="A10" s="64"/>
+      <c r="B10" s="68" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -1267,8 +1267,8 @@
       <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A11" s="68"/>
-      <c r="B11" s="62"/>
+      <c r="A11" s="64"/>
+      <c r="B11" s="68"/>
       <c r="C11" s="8" t="s">
         <v>51</v>
       </c>
@@ -1285,8 +1285,8 @@
       <c r="J11" s="18"/>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A12" s="68"/>
-      <c r="B12" s="62" t="s">
+      <c r="A12" s="64"/>
+      <c r="B12" s="68" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -1305,8 +1305,8 @@
       <c r="J12" s="18"/>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="69"/>
-      <c r="B13" s="63"/>
+      <c r="A13" s="65"/>
+      <c r="B13" s="69"/>
       <c r="C13" s="26" t="s">
         <v>52</v>
       </c>
@@ -1323,7 +1323,7 @@
       <c r="J13" s="22"/>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="13" t="s">
@@ -1346,7 +1346,7 @@
       <c r="J14" s="17"/>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A15" s="65"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="E15" s="53">
-        <v>1.4999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
@@ -1366,7 +1366,7 @@
       <c r="J15" s="18"/>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A16" s="65"/>
+      <c r="A16" s="61"/>
       <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
@@ -1386,7 +1386,7 @@
       <c r="J16" s="18"/>
     </row>
     <row r="17" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A17" s="65"/>
+      <c r="A17" s="61"/>
       <c r="B17" s="3" t="s">
         <v>32</v>
       </c>
@@ -1406,7 +1406,7 @@
       <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="66"/>
+      <c r="A18" s="62"/>
       <c r="B18" s="19" t="s">
         <v>33</v>
       </c>
@@ -1426,7 +1426,7 @@
       <c r="J18" s="22"/>
     </row>
     <row r="19" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="60" t="s">
         <v>5</v>
       </c>
       <c r="B19" s="13" t="s">
@@ -1448,7 +1448,7 @@
       <c r="J19" s="17"/>
     </row>
     <row r="20" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="65"/>
+      <c r="A20" s="61"/>
       <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
@@ -1468,7 +1468,7 @@
       <c r="J20" s="18"/>
     </row>
     <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="65"/>
+      <c r="A21" s="61"/>
       <c r="B21" s="3" t="s">
         <v>36</v>
       </c>
@@ -1488,7 +1488,7 @@
       <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A22" s="65"/>
+      <c r="A22" s="61"/>
       <c r="B22" s="3" t="s">
         <v>37</v>
       </c>
@@ -1508,7 +1508,7 @@
       <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="66"/>
+      <c r="A23" s="62"/>
       <c r="B23" s="19" t="s">
         <v>38</v>
       </c>
@@ -1528,7 +1528,7 @@
       <c r="J23" s="22"/>
     </row>
     <row r="24" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A24" s="64" t="s">
+      <c r="A24" s="60" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="13" t="s">
@@ -1550,7 +1550,7 @@
       <c r="J24" s="17"/>
     </row>
     <row r="25" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A25" s="65"/>
+      <c r="A25" s="61"/>
       <c r="B25" s="3" t="s">
         <v>40</v>
       </c>
@@ -1570,7 +1570,7 @@
       <c r="J25" s="18"/>
     </row>
     <row r="26" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="66"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="19" t="s">
         <v>41</v>
       </c>
@@ -1591,6 +1591,7 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A24:A26"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A13"/>
     <mergeCell ref="A14:A18"/>
@@ -1599,7 +1600,6 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A24:A26"/>
   </mergeCells>
   <conditionalFormatting sqref="E3">
     <cfRule type="colorScale" priority="28">

--- a/data/Program Output KPIs by $.xlsx
+++ b/data/Program Output KPIs by $.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C33D24-EA7E-4594-908F-7CCEAC3633EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336CB58B-EB5E-48B8-B20F-C8F96C274E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Research Outputs</t>
   </si>
@@ -189,9 +189,6 @@
   </si>
   <si>
     <t>Total US Dollar ($)</t>
-  </si>
-  <si>
-    <t>Notional Target</t>
   </si>
   <si>
     <t>Percentage of delivery partners trained who are female</t>
@@ -286,7 +283,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -307,12 +304,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -512,7 +503,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -587,24 +578,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -632,47 +605,23 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1048,19 +997,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436DF3B9-9B26-4648-BD64-23BB8D8864D3}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.109375" style="6" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="5" customWidth="1"/>
     <col min="3" max="3" width="66.6640625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="8.77734375" style="36" customWidth="1"/>
-    <col min="6" max="6" width="6.21875" style="12" customWidth="1"/>
-    <col min="7" max="10" width="6.21875" customWidth="1"/>
+    <col min="4" max="4" width="8.77734375" style="30" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="12" customWidth="1"/>
+    <col min="6" max="9" width="6.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="29" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="29" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28"/>
       <c r="B1" s="23" t="s">
         <v>20</v>
@@ -1068,46 +1016,42 @@
       <c r="C1" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="30" t="s">
-        <v>50</v>
+      <c r="D1" s="24">
+        <v>2025</v>
       </c>
       <c r="E1" s="24">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F1" s="24">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G1" s="24">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="H1" s="24">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="I1" s="24">
-        <v>2029</v>
-      </c>
-      <c r="J1" s="24">
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="40">
+      <c r="B2" s="32"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="34">
         <v>86973321.091999993</v>
       </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="44"/>
-    </row>
-    <row r="3" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A3" s="60" t="s">
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="38"/>
+    </row>
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A3" s="46" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -1116,214 +1060,183 @@
       <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="31">
-        <v>3</v>
-      </c>
-      <c r="E3" s="14">
-        <f>217/E2*1000000</f>
+      <c r="D3" s="14">
+        <f>217/D2*1000000</f>
         <v>2.4950179810939765</v>
       </c>
+      <c r="E3" s="15"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="G3" s="16"/>
       <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="61"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A4" s="47"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="10" t="s">
+      <c r="D4" s="10" t="s">
         <v>48</v>
       </c>
+      <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="G4" s="9"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="18"/>
-    </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="62"/>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="48"/>
       <c r="B5" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="33">
-        <v>0.11</v>
-      </c>
-      <c r="E5" s="45">
-        <f>6/E2*1000000</f>
+      <c r="D5" s="39">
+        <f>6/D2*1000000</f>
         <v>6.898667228831272E-2</v>
       </c>
+      <c r="E5" s="20"/>
       <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
+      <c r="G5" s="21"/>
       <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" s="63" t="s">
+      <c r="I5" s="22"/>
+    </row>
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A6" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="52" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="31">
-        <v>2</v>
-      </c>
-      <c r="E6" s="14">
+      <c r="D6" s="14">
         <v>1.2992489947632229</v>
       </c>
+      <c r="E6" s="15"/>
       <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+      <c r="G6" s="16"/>
       <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="17"/>
-    </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A7" s="64"/>
-      <c r="B7" s="67"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A7" s="50"/>
+      <c r="B7" s="53"/>
       <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="40">
         <v>0.59</v>
       </c>
-      <c r="E7" s="47">
-        <v>0.59</v>
-      </c>
+      <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
+      <c r="G7" s="9"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="18"/>
-    </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A8" s="64"/>
-      <c r="B8" s="68" t="s">
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A8" s="50"/>
+      <c r="B8" s="54" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="34">
-        <v>1</v>
-      </c>
-      <c r="E8" s="10">
+      <c r="D8" s="10">
         <v>1.1842712076160351</v>
       </c>
+      <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
+      <c r="G8" s="9"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="18"/>
-    </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A9" s="64"/>
-      <c r="B9" s="68"/>
+      <c r="I8" s="18"/>
+    </row>
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A9" s="50"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="48">
+      <c r="D9" s="40">
         <v>0.49</v>
       </c>
-      <c r="E9" s="47">
-        <v>0.49</v>
-      </c>
+      <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
+      <c r="G9" s="9"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="18"/>
-    </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="64"/>
-      <c r="B10" s="68" t="s">
+      <c r="I9" s="18"/>
+    </row>
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A10" s="50"/>
+      <c r="B10" s="54" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="34">
-        <v>145</v>
-      </c>
-      <c r="E10" s="10">
+      <c r="D10" s="10">
         <v>145.00998515003334</v>
       </c>
+      <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
+      <c r="G10" s="9"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="18"/>
-    </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A11" s="64"/>
-      <c r="B11" s="68"/>
+      <c r="I10" s="18"/>
+    </row>
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A11" s="50"/>
+      <c r="B11" s="54"/>
       <c r="C11" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="50">
-        <v>0.8</v>
-      </c>
-      <c r="E11" s="47">
+        <v>50</v>
+      </c>
+      <c r="D11" s="40">
         <v>0.44</v>
       </c>
+      <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
+      <c r="G11" s="9"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="18"/>
-    </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A12" s="64"/>
-      <c r="B12" s="68" t="s">
+      <c r="I11" s="18"/>
+    </row>
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A12" s="50"/>
+      <c r="B12" s="54" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="34">
-        <v>16</v>
-      </c>
-      <c r="E12" s="10">
+      <c r="D12" s="10">
         <v>16.602792464053927</v>
       </c>
+      <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="G12" s="9"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="18"/>
-    </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="65"/>
-      <c r="B13" s="69"/>
+      <c r="I12" s="18"/>
+    </row>
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="51"/>
+      <c r="B13" s="55"/>
       <c r="C13" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="51">
-        <v>0.5</v>
-      </c>
-      <c r="E13" s="49">
+        <v>51</v>
+      </c>
+      <c r="D13" s="41">
         <v>0.34</v>
       </c>
+      <c r="E13" s="20"/>
       <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
+      <c r="G13" s="21"/>
       <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="22"/>
-    </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="60" t="s">
+      <c r="I13" s="22"/>
+    </row>
+    <row r="14" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A14" s="46" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="13" t="s">
@@ -1332,101 +1245,86 @@
       <c r="C14" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="31">
-        <v>0.5</v>
-      </c>
-      <c r="E14" s="14">
-        <f>46/E2*1000000</f>
+      <c r="D14" s="14">
+        <f>46/D2*1000000</f>
         <v>0.52889782087706416</v>
       </c>
+      <c r="E14" s="15"/>
       <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
+      <c r="G14" s="16"/>
       <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="17"/>
-    </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A15" s="61"/>
+      <c r="I14" s="17"/>
+    </row>
+    <row r="15" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A15" s="47"/>
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="52">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="E15" s="53">
+        <v>52</v>
+      </c>
+      <c r="D15" s="42">
         <v>1.2E-2</v>
       </c>
+      <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
+      <c r="G15" s="9"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="18"/>
-    </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A16" s="61"/>
+      <c r="I15" s="18"/>
+    </row>
+    <row r="16" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A16" s="47"/>
       <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="50">
+      <c r="D16" s="40">
         <v>1</v>
       </c>
-      <c r="E16" s="47">
-        <v>1</v>
-      </c>
+      <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
+      <c r="G16" s="9"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="18"/>
-    </row>
-    <row r="17" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A17" s="61"/>
+      <c r="I16" s="18"/>
+    </row>
+    <row r="17" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A17" s="47"/>
       <c r="B17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="32">
-        <v>0.6</v>
-      </c>
-      <c r="E17" s="10">
+      <c r="D17" s="10">
         <v>0.58638671445065815</v>
       </c>
+      <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
+      <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="18"/>
-    </row>
-    <row r="18" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="62"/>
+      <c r="I17" s="18"/>
+    </row>
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="48"/>
       <c r="B18" s="19" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="33">
-        <v>0.31</v>
-      </c>
-      <c r="E18" s="27">
+      <c r="D18" s="27">
         <v>0.26444891043853208</v>
       </c>
+      <c r="E18" s="20"/>
       <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
+      <c r="G18" s="21"/>
       <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="22"/>
-    </row>
-    <row r="19" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A19" s="60" t="s">
+      <c r="I18" s="22"/>
+    </row>
+    <row r="19" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A19" s="46" t="s">
         <v>5</v>
       </c>
       <c r="B19" s="13" t="s">
@@ -1435,100 +1333,85 @@
       <c r="C19" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="31">
-        <v>1.6</v>
-      </c>
-      <c r="E19" s="14">
+      <c r="D19" s="14">
         <v>1.6096890200606302</v>
       </c>
+      <c r="E19" s="15"/>
       <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
+      <c r="G19" s="16"/>
       <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="17"/>
-    </row>
-    <row r="20" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="61"/>
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A20" s="47"/>
       <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="32">
-        <v>0.4</v>
-      </c>
-      <c r="E20" s="10">
+      <c r="D20" s="10">
         <v>0.43691559115931389</v>
       </c>
+      <c r="E20" s="11"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
+      <c r="G20" s="9"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="18"/>
-    </row>
-    <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="61"/>
+      <c r="I20" s="18"/>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A21" s="47"/>
       <c r="B21" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="32">
-        <v>0.13</v>
-      </c>
-      <c r="E21" s="10">
+      <c r="D21" s="10">
         <v>9.1982229717750288E-2</v>
       </c>
+      <c r="E21" s="11"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
+      <c r="G21" s="9"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="18"/>
-    </row>
-    <row r="22" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A22" s="61"/>
+      <c r="I21" s="18"/>
+    </row>
+    <row r="22" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A22" s="47"/>
       <c r="B22" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="32">
-        <v>0.41</v>
-      </c>
-      <c r="E22" s="10">
+      <c r="D22" s="10">
         <v>0.21</v>
       </c>
+      <c r="E22" s="11"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
+      <c r="G22" s="9"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="62"/>
+      <c r="I22" s="18"/>
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="48"/>
       <c r="B23" s="19" t="s">
         <v>38</v>
       </c>
       <c r="C23" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="35">
-        <v>0.22550000000000001</v>
-      </c>
-      <c r="E23" s="27">
+      <c r="D23" s="27">
         <v>0.34493336144156361</v>
       </c>
+      <c r="E23" s="20"/>
       <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
+      <c r="G23" s="21"/>
       <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="22"/>
-    </row>
-    <row r="24" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A24" s="60" t="s">
+      <c r="I23" s="22"/>
+    </row>
+    <row r="24" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A24" s="46" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="13" t="s">
@@ -1537,332 +1420,323 @@
       <c r="C24" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="54">
+      <c r="D24" s="43">
         <v>0.42</v>
       </c>
-      <c r="E24" s="55">
-        <v>0.42</v>
-      </c>
-      <c r="F24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16"/>
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="17"/>
-    </row>
-    <row r="25" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A25" s="61"/>
+      <c r="I24" s="17"/>
+    </row>
+    <row r="25" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A25" s="47"/>
       <c r="B25" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="56">
+      <c r="D25" s="44">
         <v>0.36</v>
       </c>
-      <c r="E25" s="57">
-        <v>0.36</v>
-      </c>
-      <c r="F25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" spans="1:10" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="62"/>
+      <c r="I25" s="18"/>
+    </row>
+    <row r="26" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="48"/>
       <c r="B26" s="19" t="s">
         <v>41</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="58">
-        <v>0.13</v>
-      </c>
-      <c r="E26" s="59">
+      <c r="D26" s="45">
         <v>0.11</v>
       </c>
-      <c r="F26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="21"/>
       <c r="G26" s="21"/>
       <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="22"/>
+      <c r="I26" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A13"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A19:A23"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
-  <conditionalFormatting sqref="E3">
+  <conditionalFormatting sqref="D3">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$3/2"/>
-        <cfvo type="formula" val="$D$3"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$5/2"/>
-        <cfvo type="formula" val="$D$5"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$6/2"/>
-        <cfvo type="formula" val="$D$6"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$7/2"/>
-        <cfvo type="formula" val="$D$7"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$8/2"/>
-        <cfvo type="formula" val="$D$8"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$9/2"/>
-        <cfvo type="formula" val="$D$9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10">
     <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$10/2"/>
-        <cfvo type="formula" val="$D$10"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11">
     <cfRule type="colorScale" priority="8">
       <colorScale>
-        <cfvo type="formula" val="$D$11/2"/>
-        <cfvo type="formula" val="$D$11"/>
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
         <color rgb="FF92D050"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E12">
+  <conditionalFormatting sqref="D12">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$12/2"/>
-        <cfvo type="formula" val="$D$12"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13">
     <cfRule type="colorScale" priority="7">
       <colorScale>
-        <cfvo type="formula" val="$D$13/2"/>
-        <cfvo type="formula" val="$D$13"/>
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF79B907"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
+  <conditionalFormatting sqref="D14">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$14/2"/>
-        <cfvo type="formula" val="$D$14"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E15">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$15/2"/>
-        <cfvo type="formula" val="$D$15"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$16/2"/>
-        <cfvo type="formula" val="$D$16"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17">
     <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$17/2"/>
-        <cfvo type="num" val="$D$17"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="num" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18">
     <cfRule type="colorScale" priority="13">
       <colorScale>
-        <cfvo type="formula" val="$D$18/2"/>
-        <cfvo type="formula" val="$D$18"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$19/2"/>
-        <cfvo type="formula" val="$D$19"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E20">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$20/2"/>
-        <cfvo type="formula" val="$D$20"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D21">
     <cfRule type="colorScale" priority="12">
       <colorScale>
-        <cfvo type="formula" val="$D$21/2"/>
-        <cfvo type="formula" val="$D$21"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E22">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$22/2"/>
-        <cfvo type="formula" val="$D$22"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E23">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D23">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$23/2"/>
-        <cfvo type="formula" val="$D$23"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E24">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D24">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$24/2"/>
-        <cfvo type="formula" val="$D$24"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E25">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$25/2"/>
-        <cfvo type="formula" val="$D$25"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E26">
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D26">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$D$26/2"/>
-        <cfvo type="formula" val="$D$26"/>
+        <cfvo type="formula" val="#REF!/2"/>
+        <cfvo type="formula" val="#REF!"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>

--- a/data/Program Output KPIs by $.xlsx
+++ b/data/Program Output KPIs by $.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336CB58B-EB5E-48B8-B20F-C8F96C274E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46005DDB-4F3C-438F-A2D8-BC1683C8A95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -101,9 +101,6 @@
     <t>KPI 7</t>
   </si>
   <si>
-    <t>Key Performance Indicator (KPI)</t>
-  </si>
-  <si>
     <t>Number of delivery partners trained</t>
   </si>
   <si>
@@ -198,6 +195,9 @@
   </si>
   <si>
     <t>Average (across crops) percentage yield-related genetic gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> KPI</t>
   </si>
 </sst>
 </file>
@@ -626,6 +626,18 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -642,18 +654,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1008,13 +1008,13 @@
     <col min="6" max="9" width="6.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="29" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="29" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28"/>
       <c r="B1" s="23" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D1" s="24">
         <v>2025</v>
@@ -1037,7 +1037,7 @@
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="33"/>
@@ -1051,7 +1051,7 @@
       <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -1071,7 +1071,7 @@
       <c r="I3" s="17"/>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="47"/>
+      <c r="A4" s="51"/>
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
@@ -1088,7 +1088,7 @@
       <c r="I4" s="18"/>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="48"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="19" t="s">
         <v>13</v>
       </c>
@@ -1106,14 +1106,14 @@
       <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="14">
         <v>1.2992489947632229</v>
@@ -1125,10 +1125,10 @@
       <c r="I6" s="17"/>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
-      <c r="B7" s="53"/>
+      <c r="A7" s="54"/>
+      <c r="B7" s="47"/>
       <c r="C7" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="40">
         <v>0.59</v>
@@ -1140,12 +1140,12 @@
       <c r="I7" s="18"/>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A8" s="50"/>
-      <c r="B8" s="54" t="s">
+      <c r="A8" s="54"/>
+      <c r="B8" s="48" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="10">
         <v>1.1842712076160351</v>
@@ -1157,10 +1157,10 @@
       <c r="I8" s="18"/>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A9" s="50"/>
-      <c r="B9" s="54"/>
+      <c r="A9" s="54"/>
+      <c r="B9" s="48"/>
       <c r="C9" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="40">
         <v>0.49</v>
@@ -1172,12 +1172,12 @@
       <c r="I9" s="18"/>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="50"/>
-      <c r="B10" s="54" t="s">
+      <c r="A10" s="54"/>
+      <c r="B10" s="48" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="10">
         <v>145.00998515003334</v>
@@ -1189,10 +1189,10 @@
       <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A11" s="50"/>
-      <c r="B11" s="54"/>
+      <c r="A11" s="54"/>
+      <c r="B11" s="48"/>
       <c r="C11" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="40">
         <v>0.44</v>
@@ -1204,12 +1204,12 @@
       <c r="I11" s="18"/>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A12" s="50"/>
-      <c r="B12" s="54" t="s">
+      <c r="A12" s="54"/>
+      <c r="B12" s="48" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" s="10">
         <v>16.602792464053927</v>
@@ -1221,10 +1221,10 @@
       <c r="I12" s="18"/>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="51"/>
-      <c r="B13" s="55"/>
+      <c r="A13" s="55"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="41">
         <v>0.34</v>
@@ -1236,14 +1236,14 @@
       <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="50" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" s="14">
         <f>46/D2*1000000</f>
@@ -1256,12 +1256,12 @@
       <c r="I14" s="17"/>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A15" s="47"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="42">
         <v>1.2E-2</v>
@@ -1273,12 +1273,12 @@
       <c r="I15" s="18"/>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A16" s="47"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" s="40">
         <v>1</v>
@@ -1290,9 +1290,9 @@
       <c r="I16" s="18"/>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A17" s="47"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
@@ -1307,12 +1307,12 @@
       <c r="I17" s="18"/>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="48"/>
+      <c r="A18" s="52"/>
       <c r="B18" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D18" s="27">
         <v>0.26444891043853208</v>
@@ -1324,14 +1324,14 @@
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="50" t="s">
         <v>5</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" s="14">
         <v>1.6096890200606302</v>
@@ -1343,9 +1343,9 @@
       <c r="I19" s="17"/>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="47"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>6</v>
@@ -1360,12 +1360,12 @@
       <c r="I20" s="18"/>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" s="10">
         <v>9.1982229717750288E-2</v>
@@ -1377,12 +1377,12 @@
       <c r="I21" s="18"/>
     </row>
     <row r="22" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A22" s="47"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D22" s="10">
         <v>0.21</v>
@@ -1394,12 +1394,12 @@
       <c r="I22" s="18"/>
     </row>
     <row r="23" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="48"/>
+      <c r="A23" s="52"/>
       <c r="B23" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D23" s="27">
         <v>0.34493336144156361</v>
@@ -1411,11 +1411,11 @@
       <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="50" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>8</v>
@@ -1430,9 +1430,9 @@
       <c r="I24" s="17"/>
     </row>
     <row r="25" spans="1:9" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A25" s="47"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
@@ -1447,9 +1447,9 @@
       <c r="I25" s="18"/>
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="48"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>10</v>
@@ -1465,15 +1465,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A19:A23"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="A19:A23"/>
   </mergeCells>
   <conditionalFormatting sqref="D3">
     <cfRule type="colorScale" priority="28">
